--- a/templates/Samples OGM.xlsx
+++ b/templates/Samples OGM.xlsx
@@ -29,9 +29,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A reference to one or more individuals
-associated to the material
- Select one or more items from
+          <t>Select one or more items from
 Individuals</t>
         </r>
       </text>
@@ -45,10 +43,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>An identifier associated with a
-particular source, used by the data
-provider or owner
- STRING_ARRAY: enter one or more values
+          <t>STRING_ARRAY: enter one or more values
 separated by a comma. E.g., 'value
 1','value-2',...</t>
         </r>
@@ -63,9 +58,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>One or more associations between the
-record and an organisation.
- Select one or more items from
+          <t>Select one or more items from
 Organisations</t>
         </r>
       </text>
@@ -79,11 +72,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The type of sample as characterized by
-its biological source material collected
-for testing, diagnostic, propagation,
-treatment or research purposes
- Select one item from Sample type</t>
+          <t>Select one item from Sample type</t>
         </r>
       </text>
     </comment>
@@ -96,9 +85,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>If the sample type is other, provide a
-description of the sample.
- STRING</t>
+          <t>STRING</t>
         </r>
       </text>
     </comment>
@@ -111,9 +98,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The tissue type of origin (e.g., lung or
-heart) for the sample
- Select one item from Tissue type</t>
+          <t>Select one item from Tissue type</t>
         </r>
       </text>
     </comment>
@@ -126,8 +111,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Date on which the sample was collected
- DATE (yyyy-mm-dd)</t>
+          <t>DATE (yyyy-mm-dd)</t>
         </r>
       </text>
     </comment>
@@ -140,9 +124,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The geographic location where sample
-collection took place
- Select one item from Organisations</t>
+          <t>Select one item from Organisations</t>
         </r>
       </text>
     </comment>
@@ -155,11 +137,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The number of aliquots (= pertaining to
-a portion of the whole; any one of two
-or more samples of something, of the
-same volume or weight)
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -172,10 +150,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>An ionic compound that resists changes
-in its pH. The buffer containing the
-DNA/RNA.
- Select one item from Storage buffer</t>
+          <t>Select one item from Storage buffer</t>
         </r>
       </text>
     </comment>
@@ -188,9 +163,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The conditions under which this sample
-was stored.
- Select one item from Storage conditions</t>
+          <t>Select one item from Storage conditions</t>
         </r>
       </text>
     </comment>
@@ -203,9 +176,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The determination of the volume of a
-sample.
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -218,9 +189,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>An indication of the type of unit of
-measure being used to express a volume.
- Select one item from Units</t>
+          <t>Select one item from Units</t>
         </r>
       </text>
     </comment>
@@ -233,9 +202,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Amount of input material in nanogram
-(ng).
- INTEGER</t>
+          <t>INTEGER</t>
         </r>
       </text>
     </comment>
@@ -248,10 +215,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>The number of cells (million) in a
-sample, sample volume, field, or other
-delimiter.
- DECIMAL</t>
+          <t>DECIMAL</t>
         </r>
       </text>
     </comment>
@@ -264,11 +228,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>An indication if the sample is available
-(i.e., retained, available for use,
-etc.)
- Select one item from Sample
-availability</t>
+          <t>Select one item from Sample availability</t>
         </r>
       </text>
     </comment>
@@ -281,9 +241,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>A written explanation, observation or
-criticism added to textual material
- TEXT</t>
+          <t>TEXT</t>
         </r>
       </text>
     </comment>
